--- a/outputs/reports/comparison/model_evaluation_comparison.xlsx
+++ b/outputs/reports/comparison/model_evaluation_comparison.xlsx
@@ -491,37 +491,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9906432546403512</v>
+        <v>0.9893713857357036</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2136498516320475</v>
+        <v>0.222541690626797</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9266409266409267</v>
+        <v>0.911660777385159</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3472389679286231</v>
+        <v>0.35775363993529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9908156086132263</v>
+        <v>0.9896245419488517</v>
       </c>
       <c r="G2" t="n">
-        <v>285883</v>
+        <v>257911</v>
       </c>
       <c r="H2" t="n">
-        <v>2650</v>
+        <v>2704</v>
       </c>
       <c r="I2" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
-        <v>720</v>
+        <v>774</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9762611907184625</v>
+        <v>0.9860349941936518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6669118333811218</v>
+        <v>0.6974527412588878</v>
       </c>
     </row>
     <row r="3">
@@ -531,37 +531,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9364349659534755</v>
+        <v>0.9547509408561026</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03837081302091524</v>
+        <v>0.06386020651310564</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9420849420849421</v>
+        <v>0.9469964664310954</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07373828951344817</v>
+        <v>0.1196517598035568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.936419750947032</v>
+        <v>0.9547762024442185</v>
       </c>
       <c r="G3" t="n">
-        <v>270188</v>
+        <v>248829</v>
       </c>
       <c r="H3" t="n">
-        <v>18345</v>
+        <v>11786</v>
       </c>
       <c r="I3" t="n">
         <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>732</v>
+        <v>804</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9783329722782055</v>
+        <v>0.9822966410407276</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7070085884540985</v>
+        <v>0.8596319260463616</v>
       </c>
     </row>
     <row r="4">
@@ -571,37 +571,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7242611731360824</v>
+        <v>0.7546889820395924</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007444725717349827</v>
+        <v>0.01000263227165043</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7683397683397684</v>
+        <v>0.7608951707891637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01474656654480782</v>
+        <v>0.01974569018217386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7241424724381613</v>
+        <v>0.7546687642691327</v>
       </c>
       <c r="G4" t="n">
-        <v>208939</v>
+        <v>196678</v>
       </c>
       <c r="H4" t="n">
-        <v>79594</v>
+        <v>63937</v>
       </c>
       <c r="I4" t="n">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="J4" t="n">
-        <v>597</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8378898048866475</v>
+        <v>0.8490409780236461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03159796651811853</v>
+        <v>0.04096584493647336</v>
       </c>
     </row>
     <row r="5">
@@ -611,37 +611,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9868929521966057</v>
+        <v>0.9843764342318636</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1576198046786282</v>
+        <v>0.167488697081792</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8931788931788932</v>
+        <v>0.9599528857479388</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2679536679536679</v>
+        <v>0.2852143482064742</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9871453178665872</v>
+        <v>0.9844559983116858</v>
       </c>
       <c r="G5" t="n">
-        <v>284824</v>
+        <v>256564</v>
       </c>
       <c r="H5" t="n">
-        <v>3709</v>
+        <v>4051</v>
       </c>
       <c r="I5" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>694</v>
+        <v>815</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9769659117168761</v>
+        <v>0.9921433167948055</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5475184683345096</v>
+        <v>0.7271884650078903</v>
       </c>
     </row>
     <row r="6">
@@ -651,37 +651,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9983927275241091</v>
+        <v>0.998978826913074</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6793103448275862</v>
+        <v>0.8523002421307506</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7606177606177607</v>
+        <v>0.8292108362779741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7176684881602914</v>
+        <v>0.8405970149253731</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9990330395483359</v>
+        <v>0.9995318765228403</v>
       </c>
       <c r="G6" t="n">
-        <v>288254</v>
+        <v>260493</v>
       </c>
       <c r="H6" t="n">
-        <v>279</v>
+        <v>122</v>
       </c>
       <c r="I6" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="J6" t="n">
-        <v>591</v>
+        <v>704</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9845367865663638</v>
+        <v>0.9839299458083961</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7424827721444611</v>
+        <v>0.8844066737680335</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,32 +726,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>상위1%양성포착비율(top_1pct_recall)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>상위5%건수(top_5pct_count)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>상위5%양성비율(top_5pct_positive_rate)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>상위5%리프트(top_5pct_lift)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>상위5%양성포착비율(top_5pct_recall)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>상위10%건수(top_10pct_count)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>상위10%양성비율(top_10pct_positive_rate)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>상위10%리프트(top_10pct_lift)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>상위10%양성포착비율(top_10pct_recall)</t>
         </is>
       </c>
     </row>
@@ -762,34 +777,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2460262612301313</v>
+        <v>0.2860420650095603</v>
       </c>
       <c r="E2" t="n">
-        <v>91.60599438415609</v>
+        <v>88.09152236237887</v>
       </c>
       <c r="F2" t="n">
-        <v>14466</v>
+        <v>0.8810365135453475</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05087792064150422</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>18.94400414516549</v>
+        <v>0.06218448829738412</v>
       </c>
       <c r="I2" t="n">
-        <v>28931</v>
+        <v>19.15077155263515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02547440461788393</v>
+        <v>0.9575971731448764</v>
       </c>
       <c r="K2" t="n">
-        <v>9.485199485199486</v>
+        <v>26147</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03147588633495239</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.693534917175489</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9693757361601885</v>
       </c>
     </row>
     <row r="3">
@@ -799,34 +823,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C3" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D3" t="n">
-        <v>0.241534208707671</v>
+        <v>0.2978967495219885</v>
       </c>
       <c r="E3" t="n">
-        <v>89.93341302601841</v>
+        <v>91.74237422499081</v>
       </c>
       <c r="F3" t="n">
-        <v>14466</v>
+        <v>0.917550058892815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05053228259366791</v>
+        <v>13074</v>
       </c>
       <c r="H3" t="n">
-        <v>18.81530846483149</v>
+        <v>0.06164907449900566</v>
       </c>
       <c r="I3" t="n">
-        <v>28931</v>
+        <v>18.98588176066904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02554353461684698</v>
+        <v>0.9493521790341578</v>
       </c>
       <c r="K3" t="n">
-        <v>9.51093951093951</v>
+        <v>26147</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03101694267028722</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.552195404409868</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9552414605418139</v>
       </c>
     </row>
     <row r="4">
@@ -836,34 +869,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C4" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06046993780234969</v>
+        <v>0.06806883365200765</v>
       </c>
       <c r="E4" t="n">
-        <v>22.51551828262264</v>
+        <v>20.96295585628802</v>
       </c>
       <c r="F4" t="n">
-        <v>14466</v>
+        <v>0.2096584216725559</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02274298354762892</v>
+        <v>13074</v>
       </c>
       <c r="H4" t="n">
-        <v>8.468175765977508</v>
+        <v>0.02914180816888481</v>
       </c>
       <c r="I4" t="n">
-        <v>28931</v>
+        <v>8.974715819869608</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01489751477653728</v>
+        <v>0.4487632508833923</v>
       </c>
       <c r="K4" t="n">
-        <v>5.546975546975546</v>
+        <v>26147</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0182430106704402</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.618245632433425</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5618374558303887</v>
       </c>
     </row>
     <row r="5">
@@ -873,34 +915,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C5" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2335867311679337</v>
+        <v>0.3024856596558317</v>
       </c>
       <c r="E5" t="n">
-        <v>86.97423062315944</v>
+        <v>93.15560720406641</v>
       </c>
       <c r="F5" t="n">
-        <v>14466</v>
+        <v>0.9316843345111896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05011751693626434</v>
+        <v>13074</v>
       </c>
       <c r="H5" t="n">
-        <v>18.66087364843068</v>
+        <v>0.06348477895058896</v>
       </c>
       <c r="I5" t="n">
-        <v>28931</v>
+        <v>19.55121819026713</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0254398396184024</v>
+        <v>0.9776207302709069</v>
       </c>
       <c r="K5" t="n">
-        <v>9.472329472329472</v>
+        <v>26147</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.03197307530500631</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.846652722671577</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9846878680800942</v>
       </c>
     </row>
     <row r="6">
@@ -910,34 +961,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C6" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2474084312370421</v>
+        <v>0.3024856596558317</v>
       </c>
       <c r="E6" t="n">
-        <v>92.12063480204461</v>
+        <v>93.15560720406641</v>
       </c>
       <c r="F6" t="n">
-        <v>14466</v>
+        <v>0.9316843345111896</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05101617586063874</v>
+        <v>13074</v>
       </c>
       <c r="H6" t="n">
-        <v>18.99548241729909</v>
+        <v>0.06187853755545357</v>
       </c>
       <c r="I6" t="n">
-        <v>28931</v>
+        <v>19.0565488143688</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02599287961010681</v>
+        <v>0.9528857479387515</v>
       </c>
       <c r="K6" t="n">
-        <v>9.678249678249678</v>
+        <v>26147</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03109343328106475</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.575751989870804</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9575971731448764</v>
       </c>
     </row>
   </sheetData>
@@ -988,13 +1048,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>223656</v>
+        <v>208751</v>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001386057159208785</v>
+        <v>9.580792427341666e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1007,13 +1067,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44036</v>
+        <v>33069</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002270869288763739</v>
+        <v>0.000272158214642112</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1026,13 +1086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13304</v>
+        <v>10446</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004509921828021648</v>
+        <v>0.001148765077541643</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1045,13 +1105,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3621</v>
+        <v>3979</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001104667219000276</v>
+        <v>0.004021110831867303</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1064,13 +1124,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1315</v>
+        <v>1734</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004562737642585551</v>
+        <v>0.01038062283737024</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1083,13 +1143,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>661</v>
+        <v>805</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0151285930408472</v>
+        <v>0.02608695652173913</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1102,13 +1162,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02594810379241517</v>
+        <v>0.03402646502835539</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1121,13 +1181,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>520</v>
+        <v>446</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04423076923076923</v>
+        <v>0.04708520179372197</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1140,13 +1200,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05080831408775981</v>
+        <v>0.1010989010989011</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1159,13 +1219,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="C11" t="n">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5162311955661124</v>
+        <v>0.5344</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1219,13 +1279,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>125270</v>
+        <v>144571</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>7.982757244352199e-05</v>
+        <v>7.60871820766267e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1238,13 +1298,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79807</v>
+        <v>64688</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001754232084904833</v>
+        <v>0.0002937175364828098</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1257,13 +1317,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35154</v>
+        <v>22366</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001706775900324288</v>
+        <v>0.0003129750514173299</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1276,13 +1336,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18830</v>
+        <v>10874</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004248539564524695</v>
+        <v>0.0004598123965422108</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1295,13 +1355,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11131</v>
+        <v>6356</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0006288743149761927</v>
+        <v>0.0004719949653870359</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1314,13 +1374,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7204</v>
+        <v>4267</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000694058856191005</v>
+        <v>0.0007030700726505742</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1333,13 +1393,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4693</v>
+        <v>2900</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002343916471340294</v>
+        <v>0.002758620689655172</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1352,13 +1412,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3151</v>
+        <v>2101</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003808314820691844</v>
+        <v>0.003807710613993336</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1371,13 +1431,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2004</v>
+        <v>1365</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007984031936127744</v>
+        <v>0.008058608058608059</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1390,13 +1450,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2066</v>
+        <v>1976</v>
       </c>
       <c r="C11" t="n">
-        <v>688</v>
+        <v>774</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3330106485963214</v>
+        <v>0.3917004048582996</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1480,7 +1540,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2360</v>
+        <v>2476</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1499,13 +1559,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45495</v>
+        <v>47773</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001978239366963402</v>
+        <v>0.0001255939547443116</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1518,13 +1578,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160389</v>
+        <v>145904</v>
       </c>
       <c r="C6" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001047453378972374</v>
+        <v>0.001288518477903279</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1537,13 +1597,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76692</v>
+        <v>61999</v>
       </c>
       <c r="C7" t="n">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005020080321285141</v>
+        <v>0.007177535121534218</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1556,13 +1616,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4191</v>
+        <v>3154</v>
       </c>
       <c r="C8" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04748270102600811</v>
+        <v>0.05928979074191503</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1575,13 +1635,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08743169398907104</v>
+        <v>0.1455696202531646</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1665,13 +1725,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>206993</v>
+        <v>189854</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001207770311073321</v>
+        <v>4.21376426095842e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1684,13 +1744,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43642</v>
+        <v>36229</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003437056046927272</v>
+        <v>0.0001104087885395678</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1703,13 +1763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20296</v>
+        <v>17335</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003941663381947182</v>
+        <v>0.0002307470435535045</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1722,13 +1782,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9490</v>
+        <v>8723</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00136986301369863</v>
+        <v>0.001031755130115786</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1741,13 +1801,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4470</v>
+        <v>4444</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004921700223713647</v>
+        <v>0.002025202520252025</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1760,13 +1820,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2152</v>
+        <v>2293</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01672862453531598</v>
+        <v>0.01090274749236808</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1779,13 +1839,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>932</v>
+        <v>1127</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0407725321888412</v>
+        <v>0.02484472049689441</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1798,13 +1858,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>370</v>
+        <v>484</v>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.127027027027027</v>
+        <v>0.1198347107438017</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1817,13 +1877,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>0.460093896713615</v>
+        <v>0.4822134387351779</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1836,13 +1896,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>752</v>
+        <v>722</v>
       </c>
       <c r="C11" t="n">
-        <v>475</v>
+        <v>582</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6316489361702128</v>
+        <v>0.8060941828254847</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1896,13 +1956,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>277032</v>
+        <v>249760</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001479973432672038</v>
+        <v>0.0001681614349775785</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1915,13 +1975,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10171</v>
+        <v>9327</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002752924982794219</v>
+        <v>0.001715449769486437</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1934,13 +1994,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>823</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01822600243013366</v>
+        <v>0.01734605377276669</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1953,13 +2013,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2164502164502164</v>
+        <v>0.1171875</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1972,13 +2032,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2802197802197802</v>
+        <v>0.2624113475177305</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1991,13 +2051,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>0.408284023668639</v>
+        <v>0.5338983050847458</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2010,13 +2070,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5567567567567567</v>
+        <v>0.66</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2029,13 +2089,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7365591397849462</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -2048,13 +2108,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C10" t="n">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -2067,13 +2127,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>323</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>322</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9969040247678018</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/comparison/model_evaluation_comparison.xlsx
+++ b/outputs/reports/comparison/model_evaluation_comparison.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="모델비교(model_comparison)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="상위K퍼센트(lift)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="점수구간_catboost" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="점수구간_stacked_ensemble" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="점수구간_easy_ensemble" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="점수구간_gradient_boosting" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="점수구간_random_forest" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모델비교(model_comparison)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상위K퍼센트(lift)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_catboost_v1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_stacked_ensemble_v1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_easy_ensemble_v1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_gradient_boosting_v1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v1" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,201 +487,201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9893713857357036</v>
+        <v>0.9880541750552592</v>
       </c>
       <c r="C2" t="n">
-        <v>0.222541690626797</v>
+        <v>0.2199440820130475</v>
       </c>
       <c r="D2" t="n">
-        <v>0.911660777385159</v>
+        <v>0.9535353535353536</v>
       </c>
       <c r="E2" t="n">
-        <v>0.35775363993529</v>
+        <v>0.3574403634986748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9896245419488517</v>
+        <v>0.9881748762035277</v>
       </c>
       <c r="G2" t="n">
-        <v>257911</v>
+        <v>139889</v>
       </c>
       <c r="H2" t="n">
-        <v>2704</v>
+        <v>1674</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>774</v>
+        <v>472</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9860349941936518</v>
+        <v>0.9892893031100048</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6974527412588878</v>
+        <v>0.7598629647128564</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9547509408561026</v>
+        <v>0.9549620577510595</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06386020651310564</v>
+        <v>0.07019076743847386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9469964664310954</v>
+        <v>0.9737373737373738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1196517598035568</v>
+        <v>0.1309426786199402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9547762024442185</v>
+        <v>0.9548964065469084</v>
       </c>
       <c r="G3" t="n">
-        <v>248829</v>
+        <v>135178</v>
       </c>
       <c r="H3" t="n">
-        <v>11786</v>
+        <v>6385</v>
       </c>
       <c r="I3" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>804</v>
+        <v>482</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9822966410407276</v>
+        <v>0.9904099948504206</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8596319260463616</v>
+        <v>0.964880059813097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7546889820395924</v>
+        <v>0.7351293133790424</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01000263227165043</v>
+        <v>0.01008021954823728</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7608951707891637</v>
+        <v>0.7717171717171717</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01974569018217386</v>
+        <v>0.01990049751243781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7546687642691327</v>
+        <v>0.7350013774785784</v>
       </c>
       <c r="G4" t="n">
-        <v>196678</v>
+        <v>104049</v>
       </c>
       <c r="H4" t="n">
-        <v>63937</v>
+        <v>37514</v>
       </c>
       <c r="I4" t="n">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="J4" t="n">
-        <v>646</v>
+        <v>382</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8490409780236461</v>
+        <v>0.8431200100294425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04096584493647336</v>
+        <v>0.06182051370602611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9843764342318636</v>
+        <v>0.9703149417843416</v>
       </c>
       <c r="C5" t="n">
-        <v>0.167488697081792</v>
+        <v>0.09277899343544858</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9599528857479388</v>
+        <v>0.8565656565656565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2852143482064742</v>
+        <v>0.1674234945705824</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9844559983116858</v>
+        <v>0.9707126862245078</v>
       </c>
       <c r="G5" t="n">
-        <v>256564</v>
+        <v>137417</v>
       </c>
       <c r="H5" t="n">
-        <v>4051</v>
+        <v>4146</v>
       </c>
       <c r="I5" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="J5" t="n">
-        <v>815</v>
+        <v>424</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9921433167948055</v>
+        <v>0.9626496166142824</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7271884650078903</v>
+        <v>0.7145772105801805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.998978826913074</v>
+        <v>0.9994931647636881</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8523002421307506</v>
+        <v>0.904397705544933</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8292108362779741</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8405970149253731</v>
+        <v>0.9292730844793713</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9995318765228403</v>
+        <v>0.999646800364502</v>
       </c>
       <c r="G6" t="n">
-        <v>260493</v>
+        <v>141513</v>
       </c>
       <c r="H6" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9839299458083961</v>
+        <v>0.9916065924034108</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8844066737680335</v>
+        <v>0.9677893830529142</v>
       </c>
     </row>
   </sheetData>
@@ -773,231 +773,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.003484492249644511</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>1421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2860420650095603</v>
+        <v>0.3201970443349754</v>
       </c>
       <c r="E2" t="n">
-        <v>88.09152236237887</v>
+        <v>91.89202368512714</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8810365135453475</v>
+        <v>0.9191919191919192</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>7103</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06218448829738412</v>
+        <v>0.06799943685766577</v>
       </c>
       <c r="I2" t="n">
-        <v>19.15077155263515</v>
+        <v>19.51487676995209</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.9757575757575757</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>14206</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03147588633495239</v>
+        <v>0.03407011122061101</v>
       </c>
       <c r="M2" t="n">
-        <v>9.693534917175489</v>
+        <v>9.777640120762745</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9693757361601885</v>
+        <v>0.9777777777777777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.003484492249644511</v>
       </c>
       <c r="C3" t="n">
-        <v>2615</v>
+        <v>1421</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2978967495219885</v>
+        <v>0.3391977480647431</v>
       </c>
       <c r="E3" t="n">
-        <v>91.74237422499081</v>
+        <v>97.34495695875006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.917550058892815</v>
+        <v>0.9737373737373738</v>
       </c>
       <c r="G3" t="n">
-        <v>13074</v>
+        <v>7103</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06164907449900566</v>
+        <v>0.06785865127410953</v>
       </c>
       <c r="I3" t="n">
-        <v>18.98588176066904</v>
+        <v>19.47447329837869</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9493521790341578</v>
+        <v>0.9737373737373738</v>
       </c>
       <c r="K3" t="n">
-        <v>26147</v>
+        <v>14206</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03101694267028722</v>
+        <v>0.03392932563705477</v>
       </c>
       <c r="M3" t="n">
-        <v>9.552195404409868</v>
+        <v>9.737236649189345</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9552414605418139</v>
+        <v>0.9737373737373738</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.003484492249644511</v>
       </c>
       <c r="C4" t="n">
-        <v>2615</v>
+        <v>1421</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06806883365200765</v>
+        <v>0.06052076002814919</v>
       </c>
       <c r="E4" t="n">
-        <v>20.96295585628802</v>
+        <v>17.36860227894711</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2096584216725559</v>
+        <v>0.1737373737373737</v>
       </c>
       <c r="G4" t="n">
-        <v>13074</v>
+        <v>7103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02914180816888481</v>
+        <v>0.02843868787836126</v>
       </c>
       <c r="I4" t="n">
-        <v>8.974715819869608</v>
+        <v>8.161501257826755</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4487632508833923</v>
+        <v>0.4080808080808081</v>
       </c>
       <c r="K4" t="n">
-        <v>26147</v>
+        <v>14206</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0182430106704402</v>
+        <v>0.01752780515275236</v>
       </c>
       <c r="M4" t="n">
-        <v>5.618245632433425</v>
+        <v>5.030232210888272</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5618374558303887</v>
+        <v>0.503030303030303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.003484492249644511</v>
       </c>
       <c r="C5" t="n">
-        <v>2615</v>
+        <v>1421</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3024856596558317</v>
+        <v>0.2871217452498241</v>
       </c>
       <c r="E5" t="n">
-        <v>93.15560720406641</v>
+        <v>82.39988057919093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9316843345111896</v>
+        <v>0.8242424242424242</v>
       </c>
       <c r="G5" t="n">
-        <v>13074</v>
+        <v>7103</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06348477895058896</v>
+        <v>0.06124172884696607</v>
       </c>
       <c r="I5" t="n">
-        <v>19.55121819026713</v>
+        <v>17.5755101344289</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9776207302709069</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="K5" t="n">
-        <v>26147</v>
+        <v>14206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03197307530500631</v>
+        <v>0.03188793467548923</v>
       </c>
       <c r="M5" t="n">
-        <v>9.846652722671577</v>
+        <v>9.151386311375047</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9846878680800942</v>
+        <v>0.9151515151515152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.003484492249644511</v>
       </c>
       <c r="C6" t="n">
-        <v>2615</v>
+        <v>1421</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3024856596558317</v>
+        <v>0.3391977480647431</v>
       </c>
       <c r="E6" t="n">
-        <v>93.15560720406641</v>
+        <v>97.34495695875006</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9316843345111896</v>
+        <v>0.9737373737373738</v>
       </c>
       <c r="G6" t="n">
-        <v>13074</v>
+        <v>7103</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06187853755545357</v>
+        <v>0.06785865127410953</v>
       </c>
       <c r="I6" t="n">
-        <v>19.0565488143688</v>
+        <v>19.47447329837869</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9528857479387515</v>
+        <v>0.9737373737373738</v>
       </c>
       <c r="K6" t="n">
-        <v>26147</v>
+        <v>14206</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03109343328106475</v>
+        <v>0.03392932563705477</v>
       </c>
       <c r="M6" t="n">
-        <v>9.575751989870804</v>
+        <v>9.737236649189345</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.9737373737373738</v>
       </c>
     </row>
   </sheetData>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208751</v>
+        <v>109618</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9.580792427341666e-05</v>
+        <v>8.210330420186466e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33069</v>
+        <v>18805</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000272158214642112</v>
+        <v>0.0001063546929008242</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10446</v>
+        <v>7126</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001148765077541643</v>
+        <v>0.000140331181588549</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3979</v>
+        <v>3087</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004021110831867303</v>
+        <v>0.001295756397797214</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1734</v>
+        <v>1272</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01038062283737024</v>
+        <v>0.00550314465408805</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>805</v>
+        <v>571</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02608695652173913</v>
+        <v>0.008756567425569177</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03402646502835539</v>
+        <v>0.06865671641791045</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>446</v>
+        <v>248</v>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04708520179372197</v>
+        <v>0.07661290322580645</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>455</v>
+        <v>258</v>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1010989010989011</v>
+        <v>0.09689922480620156</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1250</v>
+        <v>738</v>
       </c>
       <c r="C11" t="n">
-        <v>668</v>
+        <v>400</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5344</v>
+        <v>0.5420054200542005</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>144571</v>
+        <v>80782</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>7.60871820766267e-05</v>
+        <v>4.951598128295907e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64688</v>
+        <v>33200</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002937175364828098</v>
+        <v>0.0001807228915662651</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22366</v>
+        <v>11854</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003129750514173299</v>
+        <v>0.0002530791294077948</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10874</v>
+        <v>5814</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004598123965422108</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6356</v>
+        <v>3530</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004719949653870359</v>
+        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4267</v>
+        <v>2255</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007030700726505742</v>
+        <v>0</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2900</v>
+        <v>1519</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002758620689655172</v>
+        <v>0</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2101</v>
+        <v>1092</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003807710613993336</v>
+        <v>0</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1365</v>
+        <v>822</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008058608058608059</v>
+        <v>0.00121654501216545</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1976</v>
+        <v>1190</v>
       </c>
       <c r="C11" t="n">
-        <v>774</v>
+        <v>481</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3917004048582996</v>
+        <v>0.4042016806722689</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1525,12 +1525,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1540,7 +1544,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2476</v>
+        <v>2756</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1559,13 +1563,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47773</v>
+        <v>23109</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001255939547443116</v>
+        <v>4.327318360811805e-05</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1578,13 +1582,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>145904</v>
+        <v>77847</v>
       </c>
       <c r="C6" t="n">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001288518477903279</v>
+        <v>0.001400182409084486</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1597,13 +1601,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61999</v>
+        <v>36689</v>
       </c>
       <c r="C7" t="n">
-        <v>445</v>
+        <v>297</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007177535121534218</v>
+        <v>0.008095069366840197</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1616,13 +1620,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3154</v>
+        <v>1571</v>
       </c>
       <c r="C8" t="n">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05928979074191503</v>
+        <v>0.04455760661998727</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1635,13 +1639,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1455696202531646</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1725,13 +1729,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>189854</v>
+        <v>88405</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>4.21376426095842e-05</v>
+        <v>0.0002149199705898988</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1744,13 +1748,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36229</v>
+        <v>22820</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001104087885395678</v>
+        <v>0.0005258545135845749</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1763,13 +1767,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17335</v>
+        <v>13217</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002307470435535045</v>
+        <v>0.000529620942725278</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1782,13 +1786,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8723</v>
+        <v>8177</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001031755130115786</v>
+        <v>0.001712119359178183</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1801,13 +1805,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4444</v>
+        <v>4851</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002025202520252025</v>
+        <v>0.003710575139146568</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1820,13 +1824,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2293</v>
+        <v>2650</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01090274749236808</v>
+        <v>0.004528301886792453</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1839,13 +1843,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02484472049689441</v>
+        <v>0.01943462897526502</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1858,13 +1862,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>484</v>
+        <v>387</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1198347107438017</v>
+        <v>0.1343669250645995</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1877,13 +1881,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>179</v>
       </c>
       <c r="C10" t="n">
         <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4822134387351779</v>
+        <v>0.6815642458100558</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1896,13 +1900,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>722</v>
+        <v>240</v>
       </c>
       <c r="C11" t="n">
-        <v>582</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8060941828254847</v>
+        <v>0.9041666666666667</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1956,13 +1960,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249760</v>
+        <v>135864</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001681614349775785</v>
+        <v>9.568391921333098e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1975,13 +1979,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9327</v>
+        <v>4890</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001715449769486437</v>
+        <v>0</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1994,13 +1998,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1153</v>
+        <v>565</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01734605377276669</v>
+        <v>0.003539823008849557</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -2013,13 +2017,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1171875</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -2032,13 +2036,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2624113475177305</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2051,13 +2055,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5338983050847458</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2070,13 +2074,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.66</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2089,13 +2093,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7786885245901639</v>
+        <v>0.75</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -2108,13 +2112,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9634146341463414</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -2127,13 +2131,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>323</v>
+        <v>411</v>
       </c>
       <c r="C11" t="n">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9969040247678018</v>
+        <v>0.9975669099756691</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/comparison/model_evaluation_comparison.xlsx
+++ b/outputs/reports/comparison/model_evaluation_comparison.xlsx
@@ -10,10 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모델비교(model_comparison)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상위K퍼센트(lift)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_catboost_v1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_stacked_ensemble_v1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_easy_ensemble_v1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_gradient_boosting_v1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_catboost_v2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v2" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,197 +490,157 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9880541750552592</v>
+        <v>0.9891878040571551</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2199440820130475</v>
+        <v>0.2240652235029519</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9535353535353536</v>
+        <v>0.9224537037037037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3574403634986748</v>
+        <v>0.3605519113322778</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9881748762035277</v>
+        <v>0.9894090560245588</v>
       </c>
       <c r="G2" t="n">
-        <v>139889</v>
+        <v>257840</v>
       </c>
       <c r="H2" t="n">
-        <v>1674</v>
+        <v>2760</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="J2" t="n">
-        <v>472</v>
+        <v>797</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9892893031100048</v>
+        <v>0.9845251209814957</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7598629647128564</v>
+        <v>0.7592751825078895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9549620577510595</v>
+        <v>0.9988220175626472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07019076743847386</v>
+        <v>0.8232558139534883</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1309426786199402</v>
+        <v>0.8213457076566125</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9548964065469084</v>
+        <v>0.9994167306216424</v>
       </c>
       <c r="G3" t="n">
-        <v>135178</v>
+        <v>260448</v>
       </c>
       <c r="H3" t="n">
-        <v>6385</v>
+        <v>152</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="J3" t="n">
-        <v>482</v>
+        <v>708</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9904099948504206</v>
+        <v>0.9828040503929677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.964880059813097</v>
+        <v>0.8769798700443475</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7351293133790424</v>
+        <v>0.9969364807392223</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01008021954823728</v>
+        <v>0.5206017004578156</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7717171717171717</v>
+        <v>0.9212962962962963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01990049751243781</v>
+        <v>0.6652737150020894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7350013774785784</v>
+        <v>0.9971872601688412</v>
       </c>
       <c r="G4" t="n">
-        <v>104049</v>
+        <v>259867</v>
       </c>
       <c r="H4" t="n">
-        <v>37514</v>
+        <v>733</v>
       </c>
       <c r="I4" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>796</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8431200100294425</v>
+        <v>0.9822592095165004</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06182051370602611</v>
+        <v>0.8843746975729039</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9703149417843416</v>
+        <v>0.9987455251965853</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09277899343544858</v>
+        <v>0.8109048723897911</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8565656565656565</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1674234945705824</v>
+        <v>0.8099652375434531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9707126862245078</v>
+        <v>0.9993745203376823</v>
       </c>
       <c r="G5" t="n">
-        <v>137417</v>
+        <v>260437</v>
       </c>
       <c r="H5" t="n">
-        <v>4146</v>
+        <v>163</v>
       </c>
       <c r="I5" t="n">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="J5" t="n">
-        <v>424</v>
+        <v>699</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9626496166142824</v>
+        <v>0.9853408977857366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7145772105801805</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9994931647636881</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.904397705544933</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9555555555555556</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9292730844793713</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.999646800364502</v>
-      </c>
-      <c r="G6" t="n">
-        <v>141513</v>
-      </c>
-      <c r="H6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" t="n">
-        <v>22</v>
-      </c>
-      <c r="J6" t="n">
-        <v>473</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.9916065924034108</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.9677893830529142</v>
+        <v>0.8783294526351263</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,227 +736,181 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C2" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3201970443349754</v>
+        <v>0.297131931166348</v>
       </c>
       <c r="E2" t="n">
-        <v>91.89202368512714</v>
+        <v>89.91817505842363</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9191919191919192</v>
+        <v>0.8993055555555556</v>
       </c>
       <c r="G2" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06799943685766577</v>
+        <v>0.06348477895058896</v>
       </c>
       <c r="I2" t="n">
-        <v>19.51487676995209</v>
+        <v>19.21178731890832</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9757575757575757</v>
+        <v>0.9606481481481481</v>
       </c>
       <c r="K2" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03407011122061101</v>
+        <v>0.03204956591578384</v>
       </c>
       <c r="M2" t="n">
-        <v>9.777640120762745</v>
+        <v>9.698851507644104</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9777777777777777</v>
+        <v>0.9699074074074074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C3" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3391977480647431</v>
+        <v>0.308604206500956</v>
       </c>
       <c r="E3" t="n">
-        <v>97.34495695875006</v>
+        <v>93.38991926917357</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9340277777777778</v>
       </c>
       <c r="G3" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06785865127410953</v>
+        <v>0.06256692672479731</v>
       </c>
       <c r="I3" t="n">
-        <v>19.47447329837869</v>
+        <v>18.93402653839399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9467592592592593</v>
       </c>
       <c r="K3" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03392932563705477</v>
+        <v>0.03159062225111867</v>
       </c>
       <c r="M3" t="n">
-        <v>9.737236649189345</v>
+        <v>9.559965805863996</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9560185185185185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C4" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06052076002814919</v>
+        <v>0.3089866156787763</v>
       </c>
       <c r="E4" t="n">
-        <v>17.36860227894711</v>
+        <v>93.50564407619856</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1737373737373737</v>
+        <v>0.9351851851851852</v>
       </c>
       <c r="G4" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02843868787836126</v>
+        <v>0.0631788282086584</v>
       </c>
       <c r="I4" t="n">
-        <v>8.161501257826755</v>
+        <v>19.11920039207021</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4080808080808081</v>
+        <v>0.9560185185185185</v>
       </c>
       <c r="K4" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01752780515275236</v>
+        <v>0.03189658469422878</v>
       </c>
       <c r="M4" t="n">
-        <v>5.030232210888272</v>
+        <v>9.652556273717401</v>
       </c>
       <c r="N4" t="n">
-        <v>0.503030303030303</v>
+        <v>0.9652777777777778</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C5" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2871217452498241</v>
+        <v>0.3108986615678777</v>
       </c>
       <c r="E5" t="n">
-        <v>82.39988057919093</v>
+        <v>94.08426811132357</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8242424242424242</v>
+        <v>0.9409722222222222</v>
       </c>
       <c r="G5" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06124172884696607</v>
+        <v>0.06287287746672786</v>
       </c>
       <c r="I5" t="n">
-        <v>17.5755101344289</v>
+        <v>19.0266134652321</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.9513888888888888</v>
       </c>
       <c r="K5" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03188793467548923</v>
+        <v>0.03170535816728497</v>
       </c>
       <c r="M5" t="n">
-        <v>9.151386311375047</v>
+        <v>9.594687231309024</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9151515151515152</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.003484492249644511</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1421</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3391977480647431</v>
-      </c>
-      <c r="E6" t="n">
-        <v>97.34495695875006</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9737373737373738</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7103</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.06785865127410953</v>
-      </c>
-      <c r="I6" t="n">
-        <v>19.47447329837869</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9737373737373738</v>
-      </c>
-      <c r="K6" t="n">
-        <v>14206</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.03392932563705477</v>
-      </c>
-      <c r="M6" t="n">
-        <v>9.737236649189345</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9594907407407407</v>
       </c>
     </row>
   </sheetData>
@@ -1048,13 +961,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>109618</v>
+        <v>214020</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>8.210330420186466e-05</v>
+        <v>9.344921035417251e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1067,13 +980,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18805</v>
+        <v>30192</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001063546929008242</v>
+        <v>0.0004305776364599894</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1086,13 +999,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7126</v>
+        <v>8851</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000140331181588549</v>
+        <v>0.0014687605920235</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1105,13 +1018,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3087</v>
+        <v>3321</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001295756397797214</v>
+        <v>0.004215597711532671</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1124,13 +1037,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>1518</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00550314465408805</v>
+        <v>0.00461133069828722</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1143,13 +1056,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>571</v>
+        <v>783</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008756567425569177</v>
+        <v>0.01915708812260536</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1162,13 +1075,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>335</v>
+        <v>505</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06865671641791045</v>
+        <v>0.02574257425742574</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1181,13 +1094,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>248</v>
+        <v>422</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07661290322580645</v>
+        <v>0.03317535545023697</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1200,13 +1113,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09689922480620156</v>
+        <v>0.07610993657505286</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1219,13 +1132,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>738</v>
+        <v>1379</v>
       </c>
       <c r="C11" t="n">
-        <v>400</v>
+        <v>719</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5420054200542005</v>
+        <v>0.5213923132704859</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1279,13 +1192,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80782</v>
+        <v>248562</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>4.951598128295907e-05</v>
+        <v>0.0001850644909519557</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1298,13 +1211,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33200</v>
+        <v>10208</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001807228915662651</v>
+        <v>0.0009796238244514106</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1317,13 +1230,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11854</v>
+        <v>1341</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002530791294077948</v>
+        <v>0.01715137956748695</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1336,13 +1249,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5814</v>
+        <v>334</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.09880239520958084</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1355,13 +1268,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3530</v>
+        <v>158</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.2784810126582278</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1374,13 +1287,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2255</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.4621212121212121</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1393,13 +1306,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1519</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.6140350877192983</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1412,13 +1325,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1092</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1431,13 +1344,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>822</v>
+        <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00121654501216545</v>
+        <v>0.9567901234567902</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1450,13 +1363,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1190</v>
+        <v>330</v>
       </c>
       <c r="C11" t="n">
-        <v>481</v>
+        <v>329</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4042016806722689</v>
+        <v>0.996969696969697</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1510,12 +1423,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>255582</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0001760687372350166</v>
+      </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1525,13 +1442,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>2906</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.003441156228492774</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1544,13 +1461,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2756</v>
+        <v>834</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.004796163069544364</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1563,13 +1480,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23109</v>
+        <v>405</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4.327318360811805e-05</v>
+        <v>0.009876543209876543</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1582,13 +1499,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77847</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001400182409084486</v>
+        <v>0.02427184466019417</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1601,13 +1518,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36689</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>297</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008095069366840197</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1620,13 +1537,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1571</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04455760661998727</v>
+        <v>0.05517241379310345</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1639,13 +1556,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.07627118644067797</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1658,12 +1575,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1476510067114094</v>
+      </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1673,12 +1594,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+        <v>948</v>
+      </c>
+      <c r="C11" t="n">
+        <v>748</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7890295358649789</v>
+      </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1729,13 +1654,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88405</v>
+        <v>255455</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002149199705898988</v>
+        <v>0.0001722416864026932</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1748,13 +1673,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22820</v>
+        <v>4210</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005258545135845749</v>
+        <v>0.003800475059382423</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1767,13 +1692,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13217</v>
+        <v>576</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000529620942725278</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1786,13 +1711,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8177</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001712119359178183</v>
+        <v>0.1557788944723618</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1805,13 +1730,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4851</v>
+        <v>161</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003710575139146568</v>
+        <v>0.3291925465838509</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1824,13 +1749,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2650</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004528301886792453</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1843,13 +1768,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1132</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01943462897526502</v>
+        <v>0.5748031496062992</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1862,13 +1787,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>387</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1343669250645995</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1881,13 +1806,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6815642458100558</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1900,244 +1825,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>240</v>
+        <v>333</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9041666666666667</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>점수구간(score_bin)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>건수(count)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>양성공(positive_count)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>양성비율(positive_rate)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>마스킹여부(masked)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>135864</v>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9.568391921333098e-05</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>100-200</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4890</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>200-300</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>565</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.003539823008849557</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300-400</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>144</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.02083333333333333</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>400-500</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>72</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>500-600</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>36</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>600-700</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>700-800</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>800-900</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>34</v>
-      </c>
-      <c r="C10" t="n">
-        <v>32</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9411764705882353</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>900-1000</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>411</v>
-      </c>
-      <c r="C11" t="n">
-        <v>410</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9975669099756691</v>
+        <v>0.996996996996997</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/comparison/model_evaluation_comparison.xlsx
+++ b/outputs/reports/comparison/model_evaluation_comparison.xlsx
@@ -10,9 +10,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모델비교(model_comparison)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상위K퍼센트(lift)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_catboost_v1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_catboost_v2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_stacked_ensemble_v1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_easy_ensemble_v1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_gradient_boosting_v1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_catboost_v2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_stacked_ensemble_v2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_easy_ensemble_v2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_gradient_boosting_v2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수구간_random_forest_v2" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,157 +496,1074 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9891878040571551</v>
+        <v>0.9893713857357036</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2240652235029519</v>
+        <v>0.222541690626797</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9224537037037037</v>
+        <v>0.911660777385159</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3605519113322778</v>
+        <v>0.35775363993529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9894090560245588</v>
+        <v>0.9896245419488517</v>
       </c>
       <c r="G2" t="n">
-        <v>257840</v>
+        <v>257911</v>
       </c>
       <c r="H2" t="n">
-        <v>2760</v>
+        <v>2704</v>
       </c>
       <c r="I2" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J2" t="n">
-        <v>797</v>
+        <v>774</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9845251209814957</v>
+        <v>0.9860349941936518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7592751825078895</v>
+        <v>0.6974527412588878</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9988220175626472</v>
+        <v>0.9547509408561026</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8232558139534883</v>
+        <v>0.06386020651310564</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8194444444444444</v>
+        <v>0.9469964664310954</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8213457076566125</v>
+        <v>0.1196517598035568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9994167306216424</v>
+        <v>0.9547762024442185</v>
       </c>
       <c r="G3" t="n">
-        <v>260448</v>
+        <v>248829</v>
       </c>
       <c r="H3" t="n">
-        <v>152</v>
+        <v>11786</v>
       </c>
       <c r="I3" t="n">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>708</v>
+        <v>804</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9828040503929677</v>
+        <v>0.9822966410407276</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8769798700443475</v>
+        <v>0.8596319260463616</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9969364807392223</v>
+        <v>0.7619328091056513</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5206017004578156</v>
+        <v>0.01046101835462214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9212962962962963</v>
+        <v>0.7726737338044759</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6652737150020894</v>
+        <v>0.02064256269863746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9971872601688412</v>
+        <v>0.761897818621338</v>
       </c>
       <c r="G4" t="n">
-        <v>259867</v>
+        <v>198562</v>
       </c>
       <c r="H4" t="n">
-        <v>733</v>
+        <v>62053</v>
       </c>
       <c r="I4" t="n">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="J4" t="n">
-        <v>796</v>
+        <v>656</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9822592095165004</v>
+        <v>0.852947825889866</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8843746975729039</v>
+        <v>0.0425594226276183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9863537618945629</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1816904706157808</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9140164899882215</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.303125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9865894135026764</v>
+      </c>
+      <c r="G5" t="n">
+        <v>257120</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3495</v>
+      </c>
+      <c r="I5" t="n">
+        <v>73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>776</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9835206145868565</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7524558562078887</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.998978826913074</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8523002421307506</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8292108362779741</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8405970149253731</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9995318765228403</v>
+      </c>
+      <c r="G6" t="n">
+        <v>260493</v>
+      </c>
+      <c r="H6" t="n">
+        <v>122</v>
+      </c>
+      <c r="I6" t="n">
+        <v>145</v>
+      </c>
+      <c r="J6" t="n">
+        <v>704</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9839299458083961</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8844066737680335</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.99713153627268</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5339739190116678</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9163722025912838</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6747614917606245</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.997394624254168</v>
+      </c>
+      <c r="G7" t="n">
+        <v>259936</v>
+      </c>
+      <c r="H7" t="n">
+        <v>679</v>
+      </c>
+      <c r="I7" t="n">
+        <v>71</v>
+      </c>
+      <c r="J7" t="n">
+        <v>778</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9857038033190811</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8597675931673048</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9708487592938225</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.09622034100393466</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.950530035335689</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1747509744478129</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9709149511731865</v>
+      </c>
+      <c r="G8" t="n">
+        <v>253035</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7580</v>
+      </c>
+      <c r="I8" t="n">
+        <v>42</v>
+      </c>
+      <c r="J8" t="n">
+        <v>807</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9852749658227785</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8838400373657338</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7652640516476455</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01048170554171654</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7632508833922261</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02067942110385984</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7652706099034975</v>
+      </c>
+      <c r="G9" t="n">
+        <v>199441</v>
+      </c>
+      <c r="H9" t="n">
+        <v>61174</v>
+      </c>
+      <c r="I9" t="n">
+        <v>201</v>
+      </c>
+      <c r="J9" t="n">
+        <v>648</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8544423088930242</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.04277795762859236</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9885835143652664</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2108825121819166</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.917550058892815</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3429451904028175</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9888149185580262</v>
+      </c>
+      <c r="G10" t="n">
+        <v>257700</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2915</v>
+      </c>
+      <c r="I10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J10" t="n">
+        <v>779</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9845880859822671</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7453264652585436</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>random_forest_v2</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>0.9988870360737998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8385922330097088</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8138987043580683</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8260609683203826</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9994896686683422</v>
+      </c>
+      <c r="G11" t="n">
+        <v>260482</v>
+      </c>
+      <c r="H11" t="n">
+        <v>133</v>
+      </c>
+      <c r="I11" t="n">
+        <v>158</v>
+      </c>
+      <c r="J11" t="n">
+        <v>691</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.9828619207710347</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8841702825731377</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>점수구간(score_bin)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수(count)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>양성공(positive_count)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>양성비율(positive_rate)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>마스킹여부(masked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200-300</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1476</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300-400</t>
+        </is>
+      </c>
       <c r="B5" t="n">
-        <v>0.9987455251965853</v>
+        <v>45406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8109048723897911</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8090277777777778</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.8099652375434531</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9993745203376823</v>
-      </c>
-      <c r="G5" t="n">
-        <v>260437</v>
-      </c>
-      <c r="H5" t="n">
-        <v>163</v>
-      </c>
-      <c r="I5" t="n">
-        <v>165</v>
-      </c>
-      <c r="J5" t="n">
-        <v>699</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9853408977857366</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.8783294526351263</v>
+        <v>0.0001101176056027838</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400-500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>152035</v>
+      </c>
+      <c r="C6" t="n">
+        <v>195</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.001282599401453613</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>500-600</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>59952</v>
+      </c>
+      <c r="C7" t="n">
+        <v>459</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.007656124899919936</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>600-700</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2381</v>
+      </c>
+      <c r="C8" t="n">
+        <v>159</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06677866442671146</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>700-800</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>214</v>
+      </c>
+      <c r="C9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1448598130841121</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>800-900</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900-1000</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>점수구간(score_bin)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수(count)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>양성공(positive_count)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>양성비율(positive_rate)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>마스킹여부(masked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>215820</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0001390047261606895</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24596</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0002845991218084242</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200-300</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9667</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0008275576704251578</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300-400</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5087</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.001965795164143896</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400-500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2592</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.005787037037037037</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>500-600</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1444</v>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.007617728531855956</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>600-700</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>820</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03048780487804878</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>700-800</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>406</v>
+      </c>
+      <c r="C9" t="n">
+        <v>39</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0960591133004926</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>800-900</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>246</v>
+      </c>
+      <c r="C10" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3252032520325203</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900-1000</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>786</v>
+      </c>
+      <c r="C11" t="n">
+        <v>624</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7938931297709924</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>점수구간(score_bin)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수(count)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>양성공(positive_count)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>양성비율(positive_rate)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>마스킹여부(masked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>255911</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0001719347741988426</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3880</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.004381443298969072</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200-300</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>529</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05103969754253308</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300-400</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>173</v>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1445086705202312</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400-500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>145</v>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3103448275862069</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>500-600</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>122</v>
+      </c>
+      <c r="C7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4918032786885246</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>600-700</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>98</v>
+      </c>
+      <c r="C8" t="n">
+        <v>59</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6020408163265306</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>700-800</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>125</v>
+      </c>
+      <c r="C9" t="n">
+        <v>97</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>800-900</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>162</v>
+      </c>
+      <c r="C10" t="n">
+        <v>157</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9691358024691358</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900-1000</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>319</v>
+      </c>
+      <c r="C11" t="n">
+        <v>318</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +1577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,181 +1659,457 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.297131931166348</v>
+        <v>0.2860420650095603</v>
       </c>
       <c r="E2" t="n">
-        <v>89.91817505842363</v>
+        <v>88.09152236237887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8993055555555556</v>
+        <v>0.8810365135453475</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06348477895058896</v>
+        <v>0.06218448829738412</v>
       </c>
       <c r="I2" t="n">
-        <v>19.21178731890832</v>
+        <v>19.15077155263515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9606481481481481</v>
+        <v>0.9575971731448764</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03204956591578384</v>
+        <v>0.03147588633495239</v>
       </c>
       <c r="M2" t="n">
-        <v>9.698851507644104</v>
+        <v>9.693534917175489</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9699074074074074</v>
+        <v>0.9693757361601885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C3" t="n">
         <v>2615</v>
       </c>
       <c r="D3" t="n">
-        <v>0.308604206500956</v>
+        <v>0.2978967495219885</v>
       </c>
       <c r="E3" t="n">
-        <v>93.38991926917357</v>
+        <v>91.74237422499081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9340277777777778</v>
+        <v>0.917550058892815</v>
       </c>
       <c r="G3" t="n">
         <v>13074</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06256692672479731</v>
+        <v>0.06164907449900566</v>
       </c>
       <c r="I3" t="n">
-        <v>18.93402653839399</v>
+        <v>18.98588176066904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9467592592592593</v>
+        <v>0.9493521790341578</v>
       </c>
       <c r="K3" t="n">
         <v>26147</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03159062225111867</v>
+        <v>0.03101694267028722</v>
       </c>
       <c r="M3" t="n">
-        <v>9.559965805863996</v>
+        <v>9.552195404409868</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9560185185185185</v>
+        <v>0.9552414605418139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C4" t="n">
         <v>2615</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3089866156787763</v>
+        <v>0.07074569789674952</v>
       </c>
       <c r="E4" t="n">
-        <v>93.50564407619856</v>
+        <v>21.78734176074878</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9351851851851852</v>
+        <v>0.2179034157832744</v>
       </c>
       <c r="G4" t="n">
         <v>13074</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0631788282086584</v>
+        <v>0.02852990668502371</v>
       </c>
       <c r="I4" t="n">
-        <v>19.11920039207021</v>
+        <v>8.786270343336913</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9560185185185185</v>
+        <v>0.4393404004711425</v>
       </c>
       <c r="K4" t="n">
         <v>26147</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03189658469422878</v>
+        <v>0.01946686044288064</v>
       </c>
       <c r="M4" t="n">
-        <v>9.652556273717401</v>
+        <v>5.995150999808413</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9652777777777778</v>
+        <v>0.5995288574793876</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C5" t="n">
         <v>2615</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3108986615678777</v>
+        <v>0.2902485659655832</v>
       </c>
       <c r="E5" t="n">
-        <v>94.08426811132357</v>
+        <v>89.38698592653149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9409722222222222</v>
+        <v>0.8939929328621908</v>
       </c>
       <c r="G5" t="n">
         <v>13074</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06287287746672786</v>
+        <v>0.06096068532966192</v>
       </c>
       <c r="I5" t="n">
-        <v>19.0266134652321</v>
+        <v>18.77388059956976</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9513888888888888</v>
+        <v>0.9387514723203769</v>
       </c>
       <c r="K5" t="n">
         <v>26147</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03170535816728497</v>
+        <v>0.03116992389184228</v>
       </c>
       <c r="M5" t="n">
-        <v>9.594687231309024</v>
+        <v>9.599308575331742</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9594907407407407</v>
+        <v>0.9599528857479388</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.003247100939326255</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3024856596558317</v>
+      </c>
+      <c r="E6" t="n">
+        <v>93.15560720406641</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9316843345111896</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13074</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.06187853755545357</v>
+      </c>
+      <c r="I6" t="n">
+        <v>19.0565488143688</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9528857479387515</v>
+      </c>
+      <c r="K6" t="n">
+        <v>26147</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03109343328106475</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.575751989870804</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9575971731448764</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.003247100939326255</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3055449330783939</v>
+      </c>
+      <c r="E7" t="n">
+        <v>94.09776252345014</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9411071849234394</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13074</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.06233746366834939</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.19788292176832</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9599528857479388</v>
+      </c>
+      <c r="K7" t="n">
+        <v>26147</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03143764102956362</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.681756624445018</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9681978798586572</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.003247100939326255</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3036328871892925</v>
+      </c>
+      <c r="E8" t="n">
+        <v>93.50891544883531</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9352179034157833</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13074</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.06195502524093621</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19.08010449893539</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9540636042402827</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26147</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.03128465980800857</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9.634643453523147</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9634864546525324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.003247100939326255</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07265774378585087</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22.37618883536362</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2237926972909305</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13074</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0289123451124369</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.904048766169849</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4452296819787986</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26147</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01939036983210311</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.971594414347476</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5971731448763251</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003247100939326255</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2948374760994264</v>
+      </c>
+      <c r="E10" t="n">
+        <v>90.8002189056071</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9081272084805654</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13074</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.06180204986997093</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.03299312980221</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9517078916372202</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26147</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03113167858645351</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.587530282601273</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9587750294464076</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.003247100939326255</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3043977055449331</v>
+      </c>
+      <c r="E11" t="n">
+        <v>93.74445427868125</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9375736160188457</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13074</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.06218448829738412</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19.15077155263515</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9575971731448764</v>
+      </c>
+      <c r="K11" t="n">
+        <v>26147</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.03113167858645351</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9.587530282601273</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9587750294464076</v>
       </c>
     </row>
   </sheetData>
@@ -961,13 +2160,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>214020</v>
+        <v>208751</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>9.344921035417251e-05</v>
+        <v>9.580792427341666e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -980,13 +2179,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30192</v>
+        <v>33069</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004305776364599894</v>
+        <v>0.000272158214642112</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -999,13 +2198,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8851</v>
+        <v>10446</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0014687605920235</v>
+        <v>0.001148765077541643</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1018,13 +2217,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3321</v>
+        <v>3979</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004215597711532671</v>
+        <v>0.004021110831867303</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1037,13 +2236,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1518</v>
+        <v>1734</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00461133069828722</v>
+        <v>0.01038062283737024</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1056,13 +2255,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>783</v>
+        <v>805</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01915708812260536</v>
+        <v>0.02608695652173913</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1075,13 +2274,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02574257425742574</v>
+        <v>0.03402646502835539</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1094,13 +2293,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03317535545023697</v>
+        <v>0.04708520179372197</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1113,13 +2312,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07610993657505286</v>
+        <v>0.1010989010989011</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1132,13 +2331,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1379</v>
+        <v>1250</v>
       </c>
       <c r="C11" t="n">
-        <v>719</v>
+        <v>668</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5213923132704859</v>
+        <v>0.5344</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1192,13 +2391,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>248562</v>
+        <v>144571</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001850644909519557</v>
+        <v>7.60871820766267e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1211,13 +2410,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10208</v>
+        <v>64688</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009796238244514106</v>
+        <v>0.0002937175364828098</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1230,13 +2429,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1341</v>
+        <v>22366</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01715137956748695</v>
+        <v>0.0003129750514173299</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1249,13 +2448,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>334</v>
+        <v>10874</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09880239520958084</v>
+        <v>0.0004598123965422108</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1268,13 +2467,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>158</v>
+        <v>6356</v>
       </c>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2784810126582278</v>
+        <v>0.0004719949653870359</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1287,13 +2486,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>4267</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4621212121212121</v>
+        <v>0.0007030700726505742</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1306,13 +2505,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>2900</v>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6140350877192983</v>
+        <v>0.002758620689655172</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1325,13 +2524,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>2101</v>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.003807710613993336</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1344,13 +2543,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>1365</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9567901234567902</v>
+        <v>0.008058608058608059</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1363,13 +2562,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>330</v>
+        <v>1976</v>
       </c>
       <c r="C11" t="n">
-        <v>329</v>
+        <v>774</v>
       </c>
       <c r="D11" t="n">
-        <v>0.996969696969697</v>
+        <v>0.3917004048582996</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1423,16 +2622,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255582</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0001760687372350166</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1442,16 +2637,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2906</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.003441156228492774</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1461,13 +2652,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>834</v>
+        <v>1520</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004796163069544364</v>
+        <v>0</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1480,13 +2671,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>405</v>
+        <v>46231</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009876543209876543</v>
+        <v>0.0001297830460080898</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1499,13 +2690,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206</v>
+        <v>150337</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02427184466019417</v>
+        <v>0.001223916933289875</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1518,13 +2709,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>60571</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>469</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.007742979313532879</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1537,13 +2728,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>2579</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05517241379310345</v>
+        <v>0.0612640558355952</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1556,13 +2747,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07627118644067797</v>
+        <v>0.1415929203539823</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1575,16 +2766,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1476510067114094</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1594,16 +2781,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>948</v>
-      </c>
-      <c r="C11" t="n">
-        <v>748</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.7890295358649789</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1654,13 +2837,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255455</v>
+        <v>201296</v>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001722416864026932</v>
+        <v>0.0001142595978062157</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1673,13 +2856,244 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4210</v>
+        <v>31071</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0003218435196807312</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200-300</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14064</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.001137656427758817</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300-400</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7185</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.001530967292971468</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400-500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3569</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.003642476884281311</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>500-600</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1826</v>
+      </c>
+      <c r="C7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0104052573932092</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>600-700</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1038</v>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03275529865125241</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>700-800</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>475</v>
+      </c>
+      <c r="C9" t="n">
+        <v>49</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1031578947368421</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>800-900</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>241</v>
+      </c>
+      <c r="C10" t="n">
+        <v>99</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4107883817427386</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900-1000</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>699</v>
+      </c>
+      <c r="C11" t="n">
+        <v>575</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8226037195994278</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>점수구간(score_bin)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수(count)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>양성공(positive_count)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>양성비율(positive_rate)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>마스킹여부(masked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>249760</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0001681614349775785</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9327</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003800475059382423</v>
+        <v>0.001715449769486437</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1692,13 +3106,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>576</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.01734605377276669</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1711,13 +3125,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1557788944723618</v>
+        <v>0.1171875</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1730,13 +3144,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3291925465838509</v>
+        <v>0.2624113475177305</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1749,13 +3163,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.5338983050847458</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1768,13 +3182,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5748031496062992</v>
+        <v>0.66</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1787,13 +3201,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1806,13 +3220,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1825,13 +3239,475 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C11" t="n">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D11" t="n">
-        <v>0.996996996996997</v>
+        <v>0.9969040247678018</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>점수구간(score_bin)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수(count)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>양성공(positive_count)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>양성비율(positive_rate)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>마스킹여부(masked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>255718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0001681539821209301</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2977</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.002015451797111186</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200-300</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>749</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01068090787716956</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300-400</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>340</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02058823529411765</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400-500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>221</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02714932126696833</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>500-600</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>162</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.06172839506172839</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>600-700</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>112</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>700-800</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1075268817204301</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>800-900</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>154</v>
+      </c>
+      <c r="C10" t="n">
+        <v>34</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900-1000</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>938</v>
+      </c>
+      <c r="C11" t="n">
+        <v>719</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7665245202558635</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>점수구간(score_bin)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수(count)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>양성공(positive_count)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>양성비율(positive_rate)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>마스킹여부(masked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>174370</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.749383494867236e-05</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>54111</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0002587274306518083</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200-300</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14229</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0002811160306416474</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300-400</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6489</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0006164278008938204</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400-500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3860</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0007772020725388601</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>500-600</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0008254230293025176</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>600-700</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1716</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.002913752913752914</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>700-800</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1268</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.003154574132492113</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>800-900</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>972</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00720164609053498</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900-1000</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C11" t="n">
+        <v>789</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3894373149062191</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/comparison/model_evaluation_comparison.xlsx
+++ b/outputs/reports/comparison/model_evaluation_comparison.xlsx
@@ -496,37 +496,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9893713857357036</v>
+        <v>0.9952022821576764</v>
       </c>
       <c r="C2" t="n">
-        <v>0.222541690626797</v>
+        <v>0.4335260115606936</v>
       </c>
       <c r="D2" t="n">
-        <v>0.911660777385159</v>
+        <v>0.462962962962963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.35775363993529</v>
+        <v>0.4477611940298508</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9896245419488517</v>
+        <v>0.9974477837387364</v>
       </c>
       <c r="G2" t="n">
-        <v>257911</v>
+        <v>38300</v>
       </c>
       <c r="H2" t="n">
-        <v>2704</v>
+        <v>98</v>
       </c>
       <c r="I2" t="n">
+        <v>87</v>
+      </c>
+      <c r="J2" t="n">
         <v>75</v>
       </c>
-      <c r="J2" t="n">
-        <v>774</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.9860349941936518</v>
+        <v>0.8920347896206013</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6974527412588878</v>
+        <v>0.4370031317911339</v>
       </c>
     </row>
     <row r="3">
@@ -536,37 +536,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9547509408561026</v>
+        <v>0.9658454356846473</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06386020651310564</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9469964664310954</v>
+        <v>0.4320987654320987</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1196517598035568</v>
+        <v>0.09608785175017158</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9547762024442185</v>
+        <v>0.9680972967342049</v>
       </c>
       <c r="G3" t="n">
-        <v>248829</v>
+        <v>37173</v>
       </c>
       <c r="H3" t="n">
-        <v>11786</v>
+        <v>1225</v>
       </c>
       <c r="I3" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="J3" t="n">
-        <v>804</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9822966410407276</v>
+        <v>0.868122391276809</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8596319260463616</v>
+        <v>0.1929882545969052</v>
       </c>
     </row>
     <row r="4">
@@ -576,37 +576,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7619328091056513</v>
+        <v>0.7987811203319503</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01046101835462214</v>
+        <v>0.01568277444855285</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7726737338044759</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02064256269863746</v>
+        <v>0.03073079325421612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.761897818621338</v>
+        <v>0.7989478618678056</v>
       </c>
       <c r="G4" t="n">
-        <v>198562</v>
+        <v>30678</v>
       </c>
       <c r="H4" t="n">
-        <v>62053</v>
+        <v>7720</v>
       </c>
       <c r="I4" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>123</v>
       </c>
       <c r="K4" t="n">
-        <v>0.852947825889866</v>
+        <v>0.8633574022309547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0425594226276183</v>
+        <v>0.08791616639087821</v>
       </c>
     </row>
     <row r="5">
@@ -616,37 +616,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9863537618945629</v>
+        <v>0.995746887966805</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1816904706157808</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9140164899882215</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="E5" t="n">
-        <v>0.303125</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9865894135026764</v>
+        <v>0.9986978488462941</v>
       </c>
       <c r="G5" t="n">
-        <v>257120</v>
+        <v>38348</v>
       </c>
       <c r="H5" t="n">
-        <v>3495</v>
+        <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="J5" t="n">
-        <v>776</v>
+        <v>48</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9835206145868565</v>
+        <v>0.873887384180889</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7524558562078887</v>
+        <v>0.3178885794856454</v>
       </c>
     </row>
     <row r="6">
@@ -656,37 +656,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.998978826913074</v>
+        <v>0.9959284232365145</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8523002421307506</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8292108362779741</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8405970149253731</v>
+        <v>0.07100591715976332</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9995318765228403</v>
+        <v>0.9999739569769259</v>
       </c>
       <c r="G6" t="n">
-        <v>260493</v>
+        <v>38397</v>
       </c>
       <c r="H6" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9839299458083961</v>
+        <v>0.85722523485341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8844066737680335</v>
+        <v>0.14396523535228</v>
       </c>
     </row>
     <row r="7">
@@ -696,37 +696,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.99713153627268</v>
+        <v>0.9964211618257262</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5339739190116678</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9163722025912838</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6747614917606245</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.997394624254168</v>
+        <v>0.9988280639616647</v>
       </c>
       <c r="G7" t="n">
-        <v>259936</v>
+        <v>38353</v>
       </c>
       <c r="H7" t="n">
-        <v>679</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J7" t="n">
-        <v>778</v>
+        <v>69</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9857038033190811</v>
+        <v>0.8840862017633377</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8597675931673048</v>
+        <v>0.4766298090742189</v>
       </c>
     </row>
     <row r="8">
@@ -736,37 +736,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9708487592938225</v>
+        <v>0.987136929460581</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09622034100393466</v>
+        <v>0.1431623931623932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.950530035335689</v>
+        <v>0.4135802469135803</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1747509744478129</v>
+        <v>0.2126984126984127</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9709149511731865</v>
+        <v>0.9895567477472785</v>
       </c>
       <c r="G8" t="n">
-        <v>253035</v>
+        <v>37997</v>
       </c>
       <c r="H8" t="n">
-        <v>7580</v>
+        <v>401</v>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="J8" t="n">
-        <v>807</v>
+        <v>67</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9852749658227785</v>
+        <v>0.884181612468242</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8838400373657338</v>
+        <v>0.3192631950454666</v>
       </c>
     </row>
     <row r="9">
@@ -776,37 +776,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7652640516476455</v>
+        <v>0.7990145228215768</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01048170554171654</v>
+        <v>0.01570079142200664</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7632508833922261</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02067942110385984</v>
+        <v>0.03076538269134567</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7652706099034975</v>
+        <v>0.7991822490754726</v>
       </c>
       <c r="G9" t="n">
-        <v>199441</v>
+        <v>30687</v>
       </c>
       <c r="H9" t="n">
-        <v>61174</v>
+        <v>7711</v>
       </c>
       <c r="I9" t="n">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="J9" t="n">
-        <v>648</v>
+        <v>123</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8544423088930242</v>
+        <v>0.8636376058681039</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04277795762859236</v>
+        <v>0.07784826065444765</v>
       </c>
     </row>
     <row r="10">
@@ -816,37 +816,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9885835143652664</v>
+        <v>0.9961099585062241</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2108825121819166</v>
+        <v>0.5545454545454546</v>
       </c>
       <c r="D10" t="n">
-        <v>0.917550058892815</v>
+        <v>0.3765432098765432</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3429451904028175</v>
+        <v>0.4485294117647059</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9888149185580262</v>
+        <v>0.9987238918693682</v>
       </c>
       <c r="G10" t="n">
-        <v>257700</v>
+        <v>38349</v>
       </c>
       <c r="H10" t="n">
-        <v>2915</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="J10" t="n">
-        <v>779</v>
+        <v>61</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9845880859822671</v>
+        <v>0.8887462952995879</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7453264652585436</v>
+        <v>0.3880114589120946</v>
       </c>
     </row>
     <row r="11">
@@ -856,37 +856,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9988870360737998</v>
+        <v>0.9959284232365145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8385922330097088</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8138987043580683</v>
+        <v>0.04938271604938271</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8260609683203826</v>
+        <v>0.09248554913294797</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9994896686683422</v>
+        <v>0.9999218709307777</v>
       </c>
       <c r="G11" t="n">
-        <v>260482</v>
+        <v>38395</v>
       </c>
       <c r="H11" t="n">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J11" t="n">
-        <v>691</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9828619207710347</v>
+        <v>0.8600092661719134</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8841702825731377</v>
+        <v>0.1599838936894722</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1476</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45406</v>
+        <v>7156</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001101176056027838</v>
+        <v>0.0001397428731134712</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152035</v>
+        <v>23452</v>
       </c>
       <c r="C6" t="n">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001282599401453613</v>
+        <v>0.001620330888623572</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59952</v>
+        <v>7816</v>
       </c>
       <c r="C7" t="n">
-        <v>459</v>
+        <v>101</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007656124899919936</v>
+        <v>0.01292221084953941</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2381</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06677866442671146</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1062,16 +1062,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>214</v>
-      </c>
-      <c r="C9" t="n">
-        <v>31</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1448598130841121</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1152,13 +1148,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>215820</v>
+        <v>37270</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001390047261606895</v>
+        <v>0.001797692514086397</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1171,13 +1167,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24596</v>
+        <v>766</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002845991218084242</v>
+        <v>0.02219321148825065</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1190,13 +1186,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9667</v>
+        <v>239</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008275576704251578</v>
+        <v>0.02510460251046025</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5087</v>
+        <v>117</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001965795164143896</v>
+        <v>0.04273504273504274</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1228,13 +1224,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2592</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005787037037037037</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1247,13 +1243,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1444</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007617728531855956</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1266,13 +1262,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>820</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03048780487804878</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1285,13 +1281,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>406</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0960591133004926</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1304,13 +1300,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3252032520325203</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1323,13 +1319,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>786</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>624</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7938931297709924</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1383,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255911</v>
+        <v>37514</v>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001719347741988426</v>
+        <v>0.002452417764034761</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1402,13 +1398,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3880</v>
+        <v>874</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004381443298969072</v>
+        <v>0.03775743707093822</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1421,13 +1417,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>529</v>
+        <v>137</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05103969754253308</v>
+        <v>0.1605839416058394</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1440,13 +1436,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1445086705202312</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1459,13 +1455,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1478,13 +1474,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4918032786885246</v>
+        <v>0.625</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1497,16 +1493,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6020408163265306</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1516,16 +1508,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
-      </c>
-      <c r="C9" t="n">
-        <v>97</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.776</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1535,16 +1523,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
-      </c>
-      <c r="C10" t="n">
-        <v>157</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9691358024691358</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1538,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>319</v>
-      </c>
-      <c r="C11" t="n">
-        <v>318</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9968652037617555</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1659,43 +1639,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2860420650095603</v>
+        <v>0.2461139896373057</v>
       </c>
       <c r="E2" t="n">
-        <v>88.09152236237887</v>
+        <v>58.58120642231177</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8810365135453475</v>
+        <v>0.5864197530864198</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06218448829738412</v>
+        <v>0.05912863070539419</v>
       </c>
       <c r="I2" t="n">
-        <v>19.15077155263515</v>
+        <v>14.07407407407407</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03147588633495239</v>
+        <v>0.03060165975103734</v>
       </c>
       <c r="M2" t="n">
-        <v>9.693534917175489</v>
+        <v>7.283950617283951</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9693757361601885</v>
+        <v>0.7283950617283951</v>
       </c>
     </row>
     <row r="3">
@@ -1705,43 +1685,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C3" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2978967495219885</v>
+        <v>0.1373056994818653</v>
       </c>
       <c r="E3" t="n">
-        <v>91.74237422499081</v>
+        <v>32.68214674086867</v>
       </c>
       <c r="F3" t="n">
-        <v>0.917550058892815</v>
+        <v>0.3271604938271605</v>
       </c>
       <c r="G3" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06164907449900566</v>
+        <v>0.04512448132780083</v>
       </c>
       <c r="I3" t="n">
-        <v>18.98588176066904</v>
+        <v>10.74074074074074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9493521790341578</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="K3" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03101694267028722</v>
+        <v>0.02645228215767635</v>
       </c>
       <c r="M3" t="n">
-        <v>9.552195404409868</v>
+        <v>6.296296296296297</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9552414605418139</v>
+        <v>0.6296296296296297</v>
       </c>
     </row>
     <row r="4">
@@ -1751,43 +1731,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C4" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07074569789674952</v>
+        <v>0.08808290155440414</v>
       </c>
       <c r="E4" t="n">
-        <v>21.78734176074878</v>
+        <v>20.96590545640632</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2179034157832744</v>
+        <v>0.2098765432098765</v>
       </c>
       <c r="G4" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02852990668502371</v>
+        <v>0.04460580912863071</v>
       </c>
       <c r="I4" t="n">
-        <v>8.786270343336913</v>
+        <v>10.61728395061728</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4393404004711425</v>
+        <v>0.5308641975308642</v>
       </c>
       <c r="K4" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01946686044288064</v>
+        <v>0.02826763485477178</v>
       </c>
       <c r="M4" t="n">
-        <v>5.995150999808413</v>
+        <v>6.728395061728396</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5995288574793876</v>
+        <v>0.6728395061728395</v>
       </c>
     </row>
     <row r="5">
@@ -1797,43 +1777,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C5" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2902485659655832</v>
+        <v>0.1658031088082902</v>
       </c>
       <c r="E5" t="n">
-        <v>89.38698592653149</v>
+        <v>39.46523380029425</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8939929328621908</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="G5" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06096068532966192</v>
+        <v>0.04719917012448133</v>
       </c>
       <c r="I5" t="n">
-        <v>18.77388059956976</v>
+        <v>11.23456790123457</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9387514723203769</v>
+        <v>0.5617283950617284</v>
       </c>
       <c r="K5" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03116992389184228</v>
+        <v>0.02697095435684647</v>
       </c>
       <c r="M5" t="n">
-        <v>9.599308575331742</v>
+        <v>6.419753086419754</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9599528857479388</v>
+        <v>0.6419753086419753</v>
       </c>
     </row>
     <row r="6">
@@ -1843,43 +1823,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C6" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3024856596558317</v>
+        <v>0.1269430051813472</v>
       </c>
       <c r="E6" t="n">
-        <v>93.15560720406641</v>
+        <v>30.21556962835029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9316843345111896</v>
+        <v>0.3024691358024691</v>
       </c>
       <c r="G6" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06187853755545357</v>
+        <v>0.04201244813278009</v>
       </c>
       <c r="I6" t="n">
-        <v>19.0565488143688</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9528857479387515</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03109343328106475</v>
+        <v>0.02982365145228216</v>
       </c>
       <c r="M6" t="n">
-        <v>9.575751989870804</v>
+        <v>7.098765432098766</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.7098765432098766</v>
       </c>
     </row>
     <row r="7">
@@ -1889,43 +1869,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C7" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3055449330783939</v>
+        <v>0.2564766839378239</v>
       </c>
       <c r="E7" t="n">
-        <v>94.09776252345014</v>
+        <v>61.04778353483017</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9411071849234394</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G7" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06233746366834939</v>
+        <v>0.05757261410788381</v>
       </c>
       <c r="I7" t="n">
-        <v>19.19788292176832</v>
+        <v>13.7037037037037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9599528857479388</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="K7" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03143764102956362</v>
+        <v>0.03060165975103734</v>
       </c>
       <c r="M7" t="n">
-        <v>9.681756624445018</v>
+        <v>7.283950617283951</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9681978798586572</v>
+        <v>0.7283950617283951</v>
       </c>
     </row>
     <row r="8">
@@ -1935,43 +1915,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C8" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3036328871892925</v>
+        <v>0.1658031088082902</v>
       </c>
       <c r="E8" t="n">
-        <v>93.50891544883531</v>
+        <v>39.46523380029425</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9352179034157833</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="G8" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06195502524093621</v>
+        <v>0.0487551867219917</v>
       </c>
       <c r="I8" t="n">
-        <v>19.08010449893539</v>
+        <v>11.60493827160494</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9540636042402827</v>
+        <v>0.5802469135802469</v>
       </c>
       <c r="K8" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03128465980800857</v>
+        <v>0.02930497925311203</v>
       </c>
       <c r="M8" t="n">
-        <v>9.634643453523147</v>
+        <v>6.975308641975309</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9634864546525324</v>
+        <v>0.6975308641975309</v>
       </c>
     </row>
     <row r="9">
@@ -1981,43 +1961,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C9" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07265774378585087</v>
+        <v>0.08808290155440414</v>
       </c>
       <c r="E9" t="n">
-        <v>22.37618883536362</v>
+        <v>20.96590545640632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2237926972909305</v>
+        <v>0.2098765432098765</v>
       </c>
       <c r="G9" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0289123451124369</v>
+        <v>0.04512448132780083</v>
       </c>
       <c r="I9" t="n">
-        <v>8.904048766169849</v>
+        <v>10.74074074074074</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4452296819787986</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="K9" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01939036983210311</v>
+        <v>0.02982365145228216</v>
       </c>
       <c r="M9" t="n">
-        <v>5.971594414347476</v>
+        <v>7.098765432098766</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5971731448763251</v>
+        <v>0.7098765432098766</v>
       </c>
     </row>
     <row r="10">
@@ -2027,43 +2007,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C10" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2948374760994264</v>
+        <v>0.1917098445595855</v>
       </c>
       <c r="E10" t="n">
-        <v>90.8002189056071</v>
+        <v>45.63167658159023</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9081272084805654</v>
+        <v>0.4567901234567901</v>
       </c>
       <c r="G10" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06180204986997093</v>
+        <v>0.05549792531120332</v>
       </c>
       <c r="I10" t="n">
-        <v>19.03299312980221</v>
+        <v>13.20987654320988</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9517078916372202</v>
+        <v>0.6604938271604939</v>
       </c>
       <c r="K10" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03113167858645351</v>
+        <v>0.03137966804979253</v>
       </c>
       <c r="M10" t="n">
-        <v>9.587530282601273</v>
+        <v>7.469135802469136</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9587750294464076</v>
+        <v>0.7469135802469136</v>
       </c>
     </row>
     <row r="11">
@@ -2073,43 +2053,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C11" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3043977055449331</v>
+        <v>0.1424870466321244</v>
       </c>
       <c r="E11" t="n">
-        <v>93.74445427868125</v>
+        <v>33.91543529712787</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9375736160188457</v>
+        <v>0.3395061728395062</v>
       </c>
       <c r="G11" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06218448829738412</v>
+        <v>0.04201244813278009</v>
       </c>
       <c r="I11" t="n">
-        <v>19.15077155263515</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03113167858645351</v>
+        <v>0.02956431535269709</v>
       </c>
       <c r="M11" t="n">
-        <v>9.587530282601273</v>
+        <v>7.037037037037037</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9587750294464076</v>
+        <v>0.7037037037037037</v>
       </c>
     </row>
   </sheetData>
@@ -2160,13 +2140,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208751</v>
+        <v>37927</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D2" t="n">
-        <v>9.580792427341666e-05</v>
+        <v>0.001423787802884489</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -2179,13 +2159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33069</v>
+        <v>259</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000272158214642112</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -2198,13 +2178,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10446</v>
+        <v>99</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001148765077541643</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -2217,13 +2197,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3979</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004021110831867303</v>
+        <v>0.1132075471698113</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -2236,13 +2216,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1734</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01038062283737024</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2255,13 +2235,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>805</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02608695652173913</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2274,13 +2254,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>529</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03402646502835539</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2293,13 +2273,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>446</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04708520179372197</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -2312,13 +2292,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>455</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1010989010989011</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -2331,13 +2311,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1250</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>668</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5344</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -2391,13 +2371,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>144571</v>
+        <v>29710</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>7.60871820766267e-05</v>
+        <v>0.001312689330191855</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -2410,13 +2390,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64688</v>
+        <v>4848</v>
       </c>
       <c r="C3" t="n">
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002937175364828098</v>
+        <v>0.003919141914191419</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -2429,13 +2409,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22366</v>
+        <v>1510</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003129750514173299</v>
+        <v>0.00728476821192053</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -2448,13 +2428,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10874</v>
+        <v>716</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004598123965422108</v>
+        <v>0.01396648044692737</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -2467,13 +2447,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6356</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004719949653870359</v>
+        <v>0.02719665271966527</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2486,13 +2466,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4267</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007030700726505742</v>
+        <v>0.01095890410958904</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2505,13 +2485,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2900</v>
+        <v>311</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002758620689655172</v>
+        <v>0.02893890675241157</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2524,13 +2504,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2101</v>
+        <v>246</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003807710613993336</v>
+        <v>0.02032520325203252</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -2543,13 +2523,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1365</v>
+        <v>206</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008058608058608059</v>
+        <v>0.01941747572815534</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -2562,13 +2542,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1976</v>
+        <v>170</v>
       </c>
       <c r="C11" t="n">
-        <v>774</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3917004048582996</v>
+        <v>0.2823529411764706</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -2652,7 +2632,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1520</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2671,13 +2651,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46231</v>
+        <v>7060</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001297830460080898</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -2690,13 +2670,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150337</v>
+        <v>23546</v>
       </c>
       <c r="C6" t="n">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001223916933289875</v>
+        <v>0.001656332285738554</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2709,13 +2689,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60571</v>
+        <v>7815</v>
       </c>
       <c r="C7" t="n">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007742979313532879</v>
+        <v>0.0127959053103007</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2728,13 +2708,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2579</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0612640558355952</v>
+        <v>0.1782945736434109</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2747,16 +2727,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>226</v>
-      </c>
-      <c r="C9" t="n">
-        <v>32</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1415929203539823</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2837,13 +2813,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201296</v>
+        <v>37463</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001142595978062157</v>
+        <v>0.002242212316151937</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -2856,13 +2832,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31071</v>
+        <v>650</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003218435196807312</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -2875,13 +2851,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14064</v>
+        <v>211</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001137656427758817</v>
+        <v>0.03791469194312796</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -2894,13 +2870,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7185</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001530967292971468</v>
+        <v>0.0641025641025641</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -2913,13 +2889,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3569</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003642476884281311</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2932,13 +2908,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1826</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0104052573932092</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2951,13 +2927,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1038</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03275529865125241</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2970,13 +2946,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>475</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1031578947368421</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -2989,13 +2965,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4107883817427386</v>
+        <v>0.9</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -3008,13 +2984,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>699</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>575</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8226037195994278</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -3068,13 +3044,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249760</v>
+        <v>37179</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001681614349775785</v>
+        <v>0.002447618279136071</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -3087,13 +3063,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9327</v>
+        <v>1094</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001715449769486437</v>
+        <v>0.02285191956124314</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -3106,13 +3082,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1153</v>
+        <v>229</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01734605377276669</v>
+        <v>0.1266375545851528</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -3125,13 +3101,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1171875</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -3144,13 +3120,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2624113475177305</v>
+        <v>0.4375</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -3163,13 +3139,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5338983050847458</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -3182,16 +3158,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" t="n">
-        <v>66</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3201,16 +3173,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
-      </c>
-      <c r="C9" t="n">
-        <v>95</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7786885245901639</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3220,16 +3188,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
-      </c>
-      <c r="C10" t="n">
-        <v>158</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9634146341463414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3239,16 +3203,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>323</v>
-      </c>
-      <c r="C11" t="n">
-        <v>322</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9969040247678018</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3299,13 +3259,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255718</v>
+        <v>38228</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001681539821209301</v>
+        <v>0.001674165533117087</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -3318,13 +3278,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2977</v>
+        <v>128</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002015451797111186</v>
+        <v>0.046875</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -3337,13 +3297,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>749</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01068090787716956</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -3356,13 +3316,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02058823529411765</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -3375,13 +3335,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>221</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02714932126696833</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -3394,13 +3354,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06172839506172839</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -3413,13 +3373,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -3432,13 +3392,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1075268817204301</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -3451,13 +3411,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2207792207792208</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -3470,13 +3430,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>938</v>
+        <v>61</v>
       </c>
       <c r="C11" t="n">
-        <v>719</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7665245202558635</v>
+        <v>0.7868852459016393</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -3530,13 +3490,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174370</v>
+        <v>33670</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>9.749383494867236e-05</v>
+        <v>0.001247401247401247</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -3549,13 +3509,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54111</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002587274306518083</v>
+        <v>0.008022215365627893</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -3568,13 +3528,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14229</v>
+        <v>703</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002811160306416474</v>
+        <v>0.0128022759601707</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -3587,13 +3547,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6489</v>
+        <v>307</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0006164278008938204</v>
+        <v>0.03257328990228013</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -3606,13 +3566,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3860</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0007772020725388601</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -3625,13 +3585,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2423</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008254230293025176</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -3644,13 +3604,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1716</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002913752913752914</v>
+        <v>0.01123595505617977</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -3663,13 +3623,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1268</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003154574132492113</v>
+        <v>0.04615384615384616</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -3682,13 +3642,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>972</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00720164609053498</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -3701,13 +3661,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2026</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>789</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3894373149062191</v>
+        <v>0.4766355140186916</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
